--- a/r4-core-main/StructureDefinition-at-core-related-person.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-related-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3230" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3232" uniqueCount="477">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T05:20:34+00:00</t>
+    <t>2026-10-19T13:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -699,6 +699,12 @@
   </si>
   <si>
     <t>RelatedPerson.identifier:socialSecurityNumber.type</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>RelatedPerson.identifier:socialSecurityNumber.type.id</t>
@@ -1817,7 +1823,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="58.23828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="20.2734375" customWidth="true" bestFit="true"/>
@@ -4457,11 +4463,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4505,10 +4513,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4614,10 +4622,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4725,10 +4733,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4751,19 +4759,19 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4812,7 +4820,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4827,21 +4835,21 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4947,10 +4955,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5058,10 +5066,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5087,26 +5095,26 @@
         <v>99</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>21</v>
@@ -5145,7 +5153,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5160,21 +5168,21 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5200,13 +5208,13 @@
         <v>153</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5256,7 +5264,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5271,21 +5279,21 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5311,24 +5319,24 @@
         <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>21</v>
@@ -5367,7 +5375,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5382,21 +5390,21 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5422,14 +5430,14 @@
         <v>153</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5478,7 +5486,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5493,21 +5501,21 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5530,19 +5538,19 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5591,7 +5599,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5606,21 +5614,21 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5646,16 +5654,16 @@
         <v>153</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5704,7 +5712,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5719,18 +5727,18 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>183</v>
@@ -5759,7 +5767,7 @@
         <v>99</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M36" t="s" s="2">
         <v>185</v>
@@ -5775,10 +5783,10 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>295</v>
+        <v>21</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>188</v>
@@ -5843,7 +5851,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>192</v>
@@ -5954,7 +5962,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>200</v>
@@ -6063,7 +6071,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>207</v>
@@ -6174,10 +6182,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6283,10 +6291,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6394,10 +6402,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6423,13 +6431,13 @@
         <v>153</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6479,7 +6487,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6488,7 +6496,7 @@
         <v>85</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>97</v>
@@ -6505,10 +6513,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6534,13 +6542,13 @@
         <v>99</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6569,10 +6577,10 @@
         <v>179</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -6590,7 +6598,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6616,10 +6624,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6645,13 +6653,13 @@
         <v>143</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6701,7 +6709,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6716,7 +6724,7 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6727,10 +6735,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6756,13 +6764,13 @@
         <v>153</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6770,10 +6778,10 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>21</v>
@@ -6812,7 +6820,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6838,13 +6846,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>142</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>21</v>
@@ -6854,7 +6862,7 @@
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6951,7 +6959,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>152</v>
@@ -7060,7 +7068,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>158</v>
@@ -7171,7 +7179,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>163</v>
@@ -7284,7 +7292,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>173</v>
@@ -7347,11 +7355,13 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -7395,10 +7405,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7504,10 +7514,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7615,10 +7625,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7641,19 +7651,19 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7702,7 +7712,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7717,21 +7727,21 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7837,10 +7847,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7948,10 +7958,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7977,26 +7987,26 @@
         <v>99</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>21</v>
@@ -8035,7 +8045,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8050,21 +8060,21 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8090,13 +8100,13 @@
         <v>153</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8146,7 +8156,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8161,21 +8171,21 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8201,24 +8211,24 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>21</v>
+        <v>348</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>21</v>
@@ -8257,7 +8267,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8272,21 +8282,21 @@
         <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8312,14 +8322,14 @@
         <v>153</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8368,7 +8378,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8383,21 +8393,21 @@
         <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8420,19 +8430,19 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8481,7 +8491,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8496,21 +8506,21 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8536,16 +8546,16 @@
         <v>153</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8594,7 +8604,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8609,18 +8619,18 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>183</v>
@@ -8649,7 +8659,7 @@
         <v>99</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>185</v>
@@ -8665,10 +8675,10 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>188</v>
@@ -8733,7 +8743,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>192</v>
@@ -8844,7 +8854,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>200</v>
@@ -8953,7 +8963,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>207</v>
@@ -9064,10 +9074,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9173,10 +9183,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9284,10 +9294,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9313,13 +9323,13 @@
         <v>153</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9369,7 +9379,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9378,7 +9388,7 @@
         <v>85</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>97</v>
@@ -9395,10 +9405,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9424,13 +9434,13 @@
         <v>99</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9459,10 +9469,10 @@
         <v>179</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9480,7 +9490,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9506,10 +9516,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9535,13 +9545,13 @@
         <v>143</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9591,7 +9601,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9606,7 +9616,7 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
@@ -9617,10 +9627,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9646,13 +9656,13 @@
         <v>153</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9660,10 +9670,10 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>21</v>
@@ -9702,7 +9712,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9728,10 +9738,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9754,70 +9764,70 @@
         <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M72" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q72" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="R72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q72" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="R72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9832,10 +9842,10 @@
         <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
@@ -9843,10 +9853,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9869,17 +9879,17 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -9928,7 +9938,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>85</v>
@@ -9943,21 +9953,21 @@
         <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9983,14 +9993,14 @@
         <v>174</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10018,28 +10028,28 @@
         <v>109</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10054,21 +10064,21 @@
         <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10091,17 +10101,17 @@
         <v>86</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10150,7 +10160,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10165,21 +10175,21 @@
         <v>97</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10202,19 +10212,19 @@
         <v>86</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10263,7 +10273,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10278,21 +10288,21 @@
         <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10318,14 +10328,14 @@
         <v>105</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -10353,10 +10363,10 @@
         <v>168</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>21</v>
@@ -10374,7 +10384,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10389,21 +10399,21 @@
         <v>97</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10429,10 +10439,10 @@
         <v>153</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10509,10 +10519,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10538,10 +10548,10 @@
         <v>131</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10616,13 +10626,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>21</v>
@@ -10644,13 +10654,13 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10710,7 +10720,7 @@
         <v>78</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>136</v>
@@ -10727,10 +10737,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10756,10 +10766,10 @@
         <v>153</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10810,7 +10820,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -10836,10 +10846,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10862,13 +10872,13 @@
         <v>86</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10919,7 +10929,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -10934,7 +10944,7 @@
         <v>97</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>21</v>
@@ -10945,10 +10955,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10971,17 +10981,17 @@
         <v>86</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -11030,7 +11040,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11042,24 +11052,24 @@
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11082,17 +11092,17 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11141,7 +11151,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -11156,21 +11166,21 @@
         <v>97</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11196,10 +11206,10 @@
         <v>201</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11250,7 +11260,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11265,10 +11275,10 @@
         <v>97</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
@@ -11276,10 +11286,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11302,19 +11312,19 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -11363,7 +11373,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11378,7 +11388,7 @@
         <v>97</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>21</v>
@@ -11389,10 +11399,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11498,10 +11508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11609,14 +11619,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11638,10 +11648,10 @@
         <v>131</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>134</v>
@@ -11696,7 +11706,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -11722,10 +11732,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11751,16 +11761,16 @@
         <v>174</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -11809,7 +11819,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>85</v>
@@ -11824,7 +11834,7 @@
         <v>97</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>21</v>
@@ -11835,10 +11845,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11861,19 +11871,19 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -11922,7 +11932,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -11937,7 +11947,7 @@
         <v>97</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>21</v>

--- a/r4-core-main/StructureDefinition-at-core-related-person.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:05:38+00:00</t>
+    <t>2026-10-20T07:19:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1309,11 +1309,10 @@
 </t>
   </si>
   <si>
-    <t>Administrative Gender Addition</t>
-  </si>
-  <si>
-    <t>HL7® Austria FHIR® Core Extension for the administrative gender of a person (Patient, Practitioner, ...). 
-The extension is used to add the missing codes and is applied in case the code for administrative gender itself is set to 'other'.</t>
+    <t>Additional administrative gender (Geschlecht)</t>
+  </si>
+  <si>
+    <t>Additional administrative gender code (Geschlecht) required in Austria that is not covered by the FHIR administrative gender codes. The extension is only applied in case the administrative gender itself is set to 'other' (Ergänzung zu 'other').</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
